--- a/AAII_Financials/Quarterly/WRAP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WRAP_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/WRAP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WRAP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
   <si>
     <t>WRAP</t>
   </si>
@@ -656,250 +656,259 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>600</v>
+      </c>
+      <c r="E8" s="3">
         <v>3600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>700</v>
-      </c>
-      <c r="S8" s="3">
-        <v>300</v>
       </c>
       <c r="T8" s="3">
         <v>300</v>
       </c>
       <c r="U8" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="V8" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2000</v>
-      </c>
-      <c r="N9" s="3">
-        <v>900</v>
       </c>
       <c r="O9" s="3">
         <v>900</v>
       </c>
       <c r="P9" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q9" s="3">
         <v>700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>400</v>
-      </c>
-      <c r="S9" s="3">
-        <v>200</v>
       </c>
       <c r="T9" s="3">
         <v>200</v>
       </c>
       <c r="U9" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="V9" s="3">
+        <v>0</v>
+      </c>
+      <c r="W9" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E10" s="3">
         <v>2100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>500</v>
-      </c>
-      <c r="J10" s="3">
-        <v>700</v>
       </c>
       <c r="K10" s="3">
         <v>700</v>
@@ -908,25 +917,25 @@
         <v>700</v>
       </c>
       <c r="M10" s="3">
+        <v>700</v>
+      </c>
+      <c r="N10" s="3">
         <v>-100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>300</v>
-      </c>
-      <c r="S10" s="3">
-        <v>100</v>
       </c>
       <c r="T10" s="3">
         <v>100</v>
@@ -935,10 +944,13 @@
         <v>100</v>
       </c>
       <c r="V10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="W10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -961,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -970,61 +983,64 @@
         <v>600</v>
       </c>
       <c r="E12" s="3">
+        <v>600</v>
+      </c>
+      <c r="F12" s="3">
         <v>1000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1200</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1500</v>
       </c>
       <c r="J12" s="3">
         <v>1500</v>
       </c>
       <c r="K12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L12" s="3">
         <v>1900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1085,8 +1101,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1111,11 +1130,11 @@
       <c r="J14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>10</v>
@@ -1123,11 +1142,11 @@
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P14" s="3">
         <v>-400</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>10</v>
@@ -1147,8 +1166,11 @@
       <c r="V14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1209,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E17" s="3">
         <v>6400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,26 +1410,27 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-11700</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
@@ -1405,128 +1438,134 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-5200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1549,14 +1588,14 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>10</v>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>10</v>
@@ -1564,70 +1603,76 @@
       <c r="V22" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1688,8 +1733,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,26 +2188,29 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>11700</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
@@ -2149,105 +2218,111 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,96 +2570,100 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>16600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>20100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>35400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>15500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>17000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>19300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>21400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E42" s="3">
         <v>10000</v>
-      </c>
-      <c r="E42" s="3">
-        <v>6500</v>
       </c>
       <c r="F42" s="3">
         <v>6500</v>
       </c>
       <c r="G42" s="3">
+        <v>6500</v>
+      </c>
+      <c r="H42" s="3">
         <v>13900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>19900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>24900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>25000</v>
-      </c>
-      <c r="K42" s="3">
-        <v>30000</v>
       </c>
       <c r="L42" s="3">
         <v>30000</v>
@@ -2583,16 +2672,16 @@
         <v>30000</v>
       </c>
       <c r="N42" s="3">
+        <v>30000</v>
+      </c>
+      <c r="O42" s="3">
         <v>35000</v>
-      </c>
-      <c r="O42" s="3">
-        <v>25000</v>
       </c>
       <c r="P42" s="3">
         <v>25000</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>10</v>
+      <c r="Q42" s="3">
+        <v>25000</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>10</v>
@@ -2609,70 +2698,76 @@
       <c r="V42" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>100</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
       <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2680,93 +2775,96 @@
         <v>5800</v>
       </c>
       <c r="E44" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F44" s="3">
         <v>6500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E45" s="3">
         <v>800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>600</v>
-      </c>
-      <c r="I45" s="3">
-        <v>700</v>
       </c>
       <c r="J45" s="3">
         <v>700</v>
       </c>
       <c r="K45" s="3">
+        <v>700</v>
+      </c>
+      <c r="L45" s="3">
         <v>900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>500</v>
-      </c>
-      <c r="M45" s="3">
-        <v>800</v>
       </c>
       <c r="N45" s="3">
         <v>800</v>
@@ -2775,7 +2873,7 @@
         <v>800</v>
       </c>
       <c r="P45" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="Q45" s="3">
         <v>300</v>
@@ -2787,78 +2885,84 @@
         <v>300</v>
       </c>
       <c r="T45" s="3">
+        <v>300</v>
+      </c>
+      <c r="U45" s="3">
         <v>100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E46" s="3">
         <v>25800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>27400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>23600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>26900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>29500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>32600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>36800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>41200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>45900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>49300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>43600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>46900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>48500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>38200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>18500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>19700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>21400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>22900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2919,46 +3023,49 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E48" s="3">
         <v>700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1300</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1000</v>
       </c>
       <c r="L48" s="3">
         <v>1000</v>
       </c>
       <c r="M48" s="3">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="N48" s="3">
         <v>600</v>
       </c>
       <c r="O48" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="P48" s="3">
         <v>500</v>
@@ -2976,21 +3083,24 @@
         <v>500</v>
       </c>
       <c r="U48" s="3">
+        <v>500</v>
+      </c>
+      <c r="V48" s="3">
         <v>400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E49" s="3">
         <v>4900</v>
-      </c>
-      <c r="E49" s="3">
-        <v>2600</v>
       </c>
       <c r="F49" s="3">
         <v>2600</v>
@@ -2999,22 +3109,22 @@
         <v>2600</v>
       </c>
       <c r="H49" s="3">
-        <v>1900</v>
+        <v>2600</v>
       </c>
       <c r="I49" s="3">
         <v>1900</v>
       </c>
       <c r="J49" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="K49" s="3">
         <v>2000</v>
       </c>
       <c r="L49" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M49" s="3">
         <v>1800</v>
-      </c>
-      <c r="M49" s="3">
-        <v>1400</v>
       </c>
       <c r="N49" s="3">
         <v>1400</v>
@@ -3023,7 +3133,7 @@
         <v>1400</v>
       </c>
       <c r="P49" s="3">
-        <v>300</v>
+        <v>1400</v>
       </c>
       <c r="Q49" s="3">
         <v>300</v>
@@ -3032,7 +3142,7 @@
         <v>300</v>
       </c>
       <c r="S49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="T49" s="3">
         <v>200</v>
@@ -3043,8 +3153,11 @@
       <c r="V49" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,16 +3283,19 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>300</v>
+      </c>
+      <c r="E52" s="3">
         <v>200</v>
-      </c>
-      <c r="E52" s="3">
-        <v>100</v>
       </c>
       <c r="F52" s="3">
         <v>100</v>
@@ -3185,7 +3304,7 @@
         <v>100</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I52" s="3">
         <v>0</v>
@@ -3229,8 +3348,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,70 +3413,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E54" s="3">
         <v>31700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>30900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>30600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>32500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>35800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>40100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>44200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>48700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>51300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>45600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>48800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>49400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>39000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>19300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>20400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>22100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>23500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,70 +3530,74 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1900</v>
-      </c>
-      <c r="F57" s="3">
-        <v>1400</v>
       </c>
       <c r="G57" s="3">
         <v>1400</v>
       </c>
       <c r="H57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I57" s="3">
         <v>900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1200</v>
-      </c>
-      <c r="P57" s="3">
-        <v>800</v>
       </c>
       <c r="Q57" s="3">
         <v>800</v>
       </c>
       <c r="R57" s="3">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="S57" s="3">
         <v>400</v>
       </c>
       <c r="T57" s="3">
+        <v>400</v>
+      </c>
+      <c r="U57" s="3">
         <v>700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3501,17 +3634,17 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3" t="s">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="P58" s="3">
-        <v>200</v>
       </c>
       <c r="Q58" s="3">
         <v>200</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>10</v>
+      <c r="R58" s="3">
+        <v>200</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>10</v>
@@ -3525,132 +3658,141 @@
       <c r="V58" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E59" s="3">
         <v>9300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1700</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1200</v>
       </c>
       <c r="I59" s="3">
         <v>1200</v>
       </c>
       <c r="J59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K59" s="3">
         <v>1000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>700</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>600</v>
       </c>
       <c r="R59" s="3">
         <v>600</v>
       </c>
       <c r="S59" s="3">
+        <v>600</v>
+      </c>
+      <c r="T59" s="3">
         <v>700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>500</v>
-      </c>
-      <c r="U59" s="3">
-        <v>300</v>
       </c>
       <c r="V59" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>10800</v>
+        <v>23500</v>
       </c>
       <c r="E60" s="3">
         <v>10800</v>
       </c>
       <c r="F60" s="3">
+        <v>10800</v>
+      </c>
+      <c r="G60" s="3">
         <v>3400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3691,14 +3833,14 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>300</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3711,13 +3853,16 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>300</v>
+        <v>1800</v>
       </c>
       <c r="E62" s="3">
         <v>300</v>
@@ -3726,7 +3871,7 @@
         <v>300</v>
       </c>
       <c r="G62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H62" s="3">
         <v>400</v>
@@ -3738,16 +3883,16 @@
         <v>400</v>
       </c>
       <c r="K62" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="L62" s="3">
         <v>100</v>
       </c>
       <c r="M62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O62" s="3">
         <v>100</v>
@@ -3762,7 +3907,7 @@
         <v>100</v>
       </c>
       <c r="S62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T62" s="3">
         <v>200</v>
@@ -3771,10 +3916,13 @@
         <v>200</v>
       </c>
       <c r="V62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,70 +4113,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>11100</v>
+        <v>25300</v>
       </c>
       <c r="E66" s="3">
         <v>11100</v>
       </c>
       <c r="F66" s="3">
+        <v>11100</v>
+      </c>
+      <c r="G66" s="3">
         <v>3700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,13 +4333,16 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
@@ -4231,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,70 +4463,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-98000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-79400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-76400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-71400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-67400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-63800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-60000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-55200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-49800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-44500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-38500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-30700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-25300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-21800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-17900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-15100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-12700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-10200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-7800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-5900</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E76" s="3">
         <v>20600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>19800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>27100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>30000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>32900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>36900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>41300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>45500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>48800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>42100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>46400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>47400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>37100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>18100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>20700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>22500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,16 +5015,17 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>100</v>
+      </c>
+      <c r="E83" s="3">
         <v>300</v>
-      </c>
-      <c r="E83" s="3">
-        <v>200</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
@@ -4845,7 +5043,7 @@
         <v>200</v>
       </c>
       <c r="K83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L83" s="3">
         <v>100</v>
@@ -4860,7 +5058,7 @@
         <v>100</v>
       </c>
       <c r="P83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -4880,8 +5078,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-12100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2700</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-2100</v>
       </c>
       <c r="U89" s="3">
         <v>-2100</v>
       </c>
       <c r="V89" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="W89" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,8 +5495,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5285,49 +5505,49 @@
         <v>-200</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
       </c>
       <c r="G91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H91" s="3">
         <v>-800</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-100</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
       </c>
       <c r="J91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1000</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-200</v>
       </c>
       <c r="N91" s="3">
         <v>-200</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
       <c r="S91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T91" s="3">
         <v>-100</v>
@@ -5336,10 +5556,13 @@
         <v>-100</v>
       </c>
       <c r="V91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,52 +5688,55 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>7200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>5100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>5000</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>4900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>4700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-25100</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-100</v>
       </c>
       <c r="R94" s="3">
         <v>-100</v>
@@ -5524,8 +5753,11 @@
       <c r="V94" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5610,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,17 +6038,20 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>400</v>
+      </c>
+      <c r="E100" s="3">
         <v>9800</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
@@ -5820,46 +6065,49 @@
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>1300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>12100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>1800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>13700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>21600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5920,66 +6168,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>11100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-14600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>19900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>10700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WRAP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WRAP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
   <si>
     <t>WRAP</t>
   </si>
@@ -656,106 +656,118 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -763,194 +775,221 @@
         <v>600</v>
       </c>
       <c r="E8" s="3">
-        <v>3600</v>
+        <v>1600</v>
       </c>
       <c r="F8" s="3">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="G8" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="H8" s="3">
         <v>3600</v>
       </c>
       <c r="I8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J8" s="3">
+        <v>700</v>
+      </c>
+      <c r="K8" s="3">
+        <v>3600</v>
+      </c>
+      <c r="L8" s="3">
         <v>1700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="M8" s="3">
         <v>1200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="N8" s="3">
         <v>1600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="O8" s="3">
         <v>2400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="P8" s="3">
         <v>1800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="Q8" s="3">
         <v>1900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="R8" s="3">
         <v>1500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="S8" s="3">
         <v>1400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="T8" s="3">
         <v>1000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="U8" s="3">
         <v>800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="V8" s="3">
         <v>700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="W8" s="3">
         <v>300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="X8" s="3">
         <v>300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Y8" s="3">
         <v>100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Z8" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>600</v>
+      </c>
+      <c r="F9" s="3">
+        <v>600</v>
+      </c>
+      <c r="G9" s="3">
         <v>900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="H9" s="3">
         <v>1500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="I9" s="3">
         <v>500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="J9" s="3">
         <v>400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="K9" s="3">
         <v>1900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="L9" s="3">
         <v>800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="M9" s="3">
         <v>700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="N9" s="3">
         <v>900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="O9" s="3">
         <v>1700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="P9" s="3">
         <v>1100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="Q9" s="3">
         <v>2000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="R9" s="3">
         <v>900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="S9" s="3">
         <v>900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="T9" s="3">
         <v>700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="U9" s="3">
         <v>600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="V9" s="3">
         <v>400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="W9" s="3">
         <v>200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="X9" s="3">
         <v>200</v>
       </c>
-      <c r="V9" s="3">
-        <v>0</v>
-      </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>800</v>
+      </c>
+      <c r="G10" s="3">
         <v>-300</v>
       </c>
-      <c r="E10" s="3">
-        <v>2100</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I10" s="3">
         <v>700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="J10" s="3">
+        <v>400</v>
+      </c>
+      <c r="K10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L10" s="3">
+        <v>900</v>
+      </c>
+      <c r="M10" s="3">
+        <v>500</v>
+      </c>
+      <c r="N10" s="3">
+        <v>700</v>
+      </c>
+      <c r="O10" s="3">
+        <v>700</v>
+      </c>
+      <c r="P10" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R10" s="3">
+        <v>600</v>
+      </c>
+      <c r="S10" s="3">
+        <v>500</v>
+      </c>
+      <c r="T10" s="3">
         <v>300</v>
       </c>
-      <c r="H10" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I10" s="3">
-        <v>900</v>
-      </c>
-      <c r="J10" s="3">
-        <v>500</v>
-      </c>
-      <c r="K10" s="3">
-        <v>700</v>
-      </c>
-      <c r="L10" s="3">
-        <v>700</v>
-      </c>
-      <c r="M10" s="3">
-        <v>700</v>
-      </c>
-      <c r="N10" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O10" s="3">
-        <v>600</v>
-      </c>
-      <c r="P10" s="3">
-        <v>500</v>
-      </c>
-      <c r="Q10" s="3">
+      <c r="U10" s="3">
+        <v>200</v>
+      </c>
+      <c r="V10" s="3">
         <v>300</v>
       </c>
-      <c r="R10" s="3">
-        <v>200</v>
-      </c>
-      <c r="S10" s="3">
-        <v>300</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="W10" s="3">
         <v>100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="X10" s="3">
         <v>100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Y10" s="3">
         <v>100</v>
       </c>
-      <c r="W10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,73 +1013,85 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>500</v>
+      </c>
+      <c r="E12" s="3">
+        <v>700</v>
+      </c>
+      <c r="F12" s="3">
+        <v>800</v>
+      </c>
+      <c r="G12" s="3">
         <v>600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="H12" s="3">
         <v>600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="I12" s="3">
         <v>1000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="J12" s="3">
         <v>1100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="K12" s="3">
         <v>900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="L12" s="3">
         <v>1200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="M12" s="3">
         <v>1500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="N12" s="3">
         <v>1500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="O12" s="3">
         <v>1900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="P12" s="3">
         <v>2100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="Q12" s="3">
         <v>1200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="R12" s="3">
         <v>1100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="S12" s="3">
         <v>800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="T12" s="3">
         <v>900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="U12" s="3">
         <v>600</v>
-      </c>
-      <c r="S12" s="3">
-        <v>500</v>
-      </c>
-      <c r="T12" s="3">
-        <v>600</v>
-      </c>
-      <c r="U12" s="3">
-        <v>700</v>
       </c>
       <c r="V12" s="3">
         <v>500</v>
       </c>
       <c r="W12" s="3">
+        <v>600</v>
+      </c>
+      <c r="X12" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1104,8 +1155,17 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1118,8 +1178,8 @@
       <c r="F14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="G14" s="3">
+        <v>-200</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>10</v>
@@ -1133,8 +1193,8 @@
       <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>10</v>
@@ -1142,21 +1202,21 @@
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S14" s="3">
         <v>-400</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1169,31 +1229,40 @@
       <c r="W14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1234,8 +1303,17 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1334,159 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F17" s="3">
+        <v>5600</v>
+      </c>
+      <c r="G17" s="3">
+        <v>7400</v>
+      </c>
+      <c r="H17" s="3">
+        <v>6400</v>
+      </c>
+      <c r="I17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="J17" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K17" s="3">
         <v>7200</v>
       </c>
-      <c r="E17" s="3">
-        <v>6400</v>
-      </c>
-      <c r="F17" s="3">
-        <v>6300</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="L17" s="3">
+        <v>5600</v>
+      </c>
+      <c r="M17" s="3">
+        <v>5900</v>
+      </c>
+      <c r="N17" s="3">
+        <v>7000</v>
+      </c>
+      <c r="O17" s="3">
+        <v>7700</v>
+      </c>
+      <c r="P17" s="3">
+        <v>7800</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>9700</v>
+      </c>
+      <c r="R17" s="3">
+        <v>7000</v>
+      </c>
+      <c r="S17" s="3">
         <v>5000</v>
       </c>
-      <c r="H17" s="3">
-        <v>7200</v>
-      </c>
-      <c r="I17" s="3">
-        <v>5600</v>
-      </c>
-      <c r="J17" s="3">
-        <v>5900</v>
-      </c>
-      <c r="K17" s="3">
-        <v>7000</v>
-      </c>
-      <c r="L17" s="3">
-        <v>7700</v>
-      </c>
-      <c r="M17" s="3">
-        <v>7800</v>
-      </c>
-      <c r="N17" s="3">
-        <v>9700</v>
-      </c>
-      <c r="O17" s="3">
-        <v>7000</v>
-      </c>
-      <c r="P17" s="3">
-        <v>5000</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="T17" s="3">
         <v>4900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="U17" s="3">
         <v>3700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="V17" s="3">
         <v>3100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="W17" s="3">
         <v>2900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="X17" s="3">
         <v>2800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Y17" s="3">
         <v>2000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Z17" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-6600</v>
+        <v>-3600</v>
       </c>
       <c r="E18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="H18" s="3">
         <v>-2800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="I18" s="3">
         <v>-5100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="J18" s="3">
         <v>-4300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="K18" s="3">
         <v>-3600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="L18" s="3">
         <v>-3900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="M18" s="3">
         <v>-4700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="N18" s="3">
         <v>-5400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="O18" s="3">
         <v>-5300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="P18" s="3">
         <v>-6000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="Q18" s="3">
         <v>-7800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="R18" s="3">
         <v>-5500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="S18" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="T18" s="3">
         <v>-3900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="U18" s="3">
         <v>-2900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="V18" s="3">
         <v>-2400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="W18" s="3">
         <v>-2600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="X18" s="3">
         <v>-2500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Y18" s="3">
         <v>-1900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Z18" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,22 +1510,25 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-11700</v>
+        <v>-5600</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-2700</v>
       </c>
       <c r="F20" s="3">
-        <v>100</v>
+        <v>-4200</v>
       </c>
       <c r="G20" s="3">
-        <v>200</v>
+        <v>11700</v>
       </c>
       <c r="H20" s="3">
         <v>100</v>
@@ -1438,10 +1540,10 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1476,78 +1578,96 @@
       <c r="W20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-18200</v>
+        <v>2200</v>
       </c>
       <c r="E21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F21" s="3">
+        <v>300</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="R21" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="S21" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="T21" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="U21" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="V21" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="W21" s="3">
         <v>-2500</v>
       </c>
-      <c r="F21" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-7700</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="T21" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="X21" s="3">
         <v>-2400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="Y21" s="3">
         <v>-1900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Z21" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>10</v>
@@ -1567,14 +1687,14 @@
       <c r="J22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1591,111 +1711,129 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>10</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>10</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z22" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F23" s="3">
+        <v>100</v>
+      </c>
+      <c r="G23" s="3">
         <v>-18400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="H23" s="3">
         <v>-2800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="I23" s="3">
         <v>-5000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="J23" s="3">
         <v>-4000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="K23" s="3">
         <v>-3500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="L23" s="3">
         <v>-3900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="M23" s="3">
         <v>-4800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="N23" s="3">
         <v>-5400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="O23" s="3">
         <v>-5200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="P23" s="3">
         <v>-6000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="Q23" s="3">
         <v>-7800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="R23" s="3">
         <v>-5400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="S23" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="T23" s="3">
         <v>-3900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="U23" s="3">
         <v>-2800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="V23" s="3">
         <v>-2300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="W23" s="3">
         <v>-2500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="X23" s="3">
         <v>-2400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="Y23" s="3">
         <v>-1900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Z23" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1736,8 +1874,17 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1948,165 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F26" s="3">
+        <v>100</v>
+      </c>
+      <c r="G26" s="3">
         <v>-18400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="H26" s="3">
         <v>-2800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="I26" s="3">
         <v>-5000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="J26" s="3">
         <v>-4000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="K26" s="3">
         <v>-3500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="L26" s="3">
         <v>-3900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="M26" s="3">
         <v>-4800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="N26" s="3">
         <v>-5400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="O26" s="3">
         <v>-5200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="P26" s="3">
         <v>-6000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="Q26" s="3">
         <v>-7800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="R26" s="3">
         <v>-5400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="S26" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="T26" s="3">
         <v>-3900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="U26" s="3">
         <v>-2800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="V26" s="3">
         <v>-2300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="W26" s="3">
         <v>-2500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="X26" s="3">
         <v>-2400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="Y26" s="3">
         <v>-1900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Z26" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-18800</v>
+        <v>1700</v>
       </c>
       <c r="E27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-18600</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="O27" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="P27" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="R27" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="S27" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="T27" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="U27" s="3">
         <v>-2800</v>
       </c>
-      <c r="F27" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-5400</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-5400</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="S27" s="3">
+      <c r="V27" s="3">
         <v>-2300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="W27" s="3">
         <v>-2500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="X27" s="3">
         <v>-2400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="Y27" s="3">
         <v>-1900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Z27" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2170,17 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2244,17 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2318,17 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,22 +2392,31 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>11700</v>
+        <v>5600</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="F32" s="3">
-        <v>-100</v>
+        <v>4200</v>
       </c>
       <c r="G32" s="3">
-        <v>-200</v>
+        <v>-11700</v>
       </c>
       <c r="H32" s="3">
         <v>-100</v>
@@ -2218,10 +2428,10 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -2256,73 +2466,91 @@
       <c r="W32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-18800</v>
+        <v>2000</v>
       </c>
       <c r="E33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F33" s="3">
+        <v>100</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="H33" s="3">
         <v>-2800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="I33" s="3">
         <v>-5000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="J33" s="3">
         <v>-4000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="K33" s="3">
         <v>-3500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="L33" s="3">
         <v>-3900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="M33" s="3">
         <v>-4800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="N33" s="3">
         <v>-5400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="O33" s="3">
         <v>-5200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="P33" s="3">
         <v>-6000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="Q33" s="3">
         <v>-7800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="R33" s="3">
         <v>-5400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="S33" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="T33" s="3">
         <v>-3900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="U33" s="3">
         <v>-2800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="V33" s="3">
         <v>-2300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="W33" s="3">
         <v>-2500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="X33" s="3">
         <v>-2400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="Y33" s="3">
         <v>-1900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Z33" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2614,170 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-18800</v>
+        <v>2000</v>
       </c>
       <c r="E35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F35" s="3">
+        <v>100</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="H35" s="3">
         <v>-2800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="I35" s="3">
         <v>-5000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="J35" s="3">
         <v>-4000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="K35" s="3">
         <v>-3500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="L35" s="3">
         <v>-3900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="M35" s="3">
         <v>-4800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="N35" s="3">
         <v>-5400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="O35" s="3">
         <v>-5200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="P35" s="3">
         <v>-6000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="Q35" s="3">
         <v>-7800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="R35" s="3">
         <v>-5400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="S35" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="T35" s="3">
         <v>-3900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="U35" s="3">
         <v>-2800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="V35" s="3">
         <v>-2300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="W35" s="3">
         <v>-2500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="X35" s="3">
         <v>-2400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="Y35" s="3">
         <v>-1900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Z35" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2801,11 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,127 +2829,139 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F41" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G41" s="3">
         <v>4000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="H41" s="3">
         <v>4900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
         <v>11700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="J41" s="3">
         <v>9500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="K41" s="3">
         <v>5300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="L41" s="3">
         <v>3800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3">
         <v>3600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>5000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="O41" s="3">
         <v>4900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="P41" s="3">
         <v>9900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="Q41" s="3">
         <v>13100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="R41" s="3">
         <v>2000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="S41" s="3">
         <v>16600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="T41" s="3">
         <v>20100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="U41" s="3">
         <v>35400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="V41" s="3">
         <v>15500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="W41" s="3">
         <v>17000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="X41" s="3">
         <v>19300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="Y41" s="3">
         <v>21400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Z41" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F42" s="3">
+        <v>5000</v>
+      </c>
+      <c r="G42" s="3">
         <v>7500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="H42" s="3">
         <v>10000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="I42" s="3">
         <v>6500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="J42" s="3">
         <v>6500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="K42" s="3">
         <v>13900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="L42" s="3">
         <v>19900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="M42" s="3">
         <v>24900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="N42" s="3">
         <v>25000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="O42" s="3">
         <v>30000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="P42" s="3">
         <v>30000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="Q42" s="3">
         <v>30000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="R42" s="3">
         <v>35000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="S42" s="3">
         <v>25000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="T42" s="3">
         <v>25000</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>10</v>
       </c>
@@ -2701,291 +2971,336 @@
       <c r="W42" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z42" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F43" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G43" s="3">
         <v>3000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="H43" s="3">
         <v>4300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="I43" s="3">
         <v>1900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="J43" s="3">
         <v>1200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="K43" s="3">
         <v>2800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="L43" s="3">
         <v>2200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="M43" s="3">
         <v>1400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="N43" s="3">
         <v>4200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="O43" s="3">
         <v>3900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="P43" s="3">
         <v>3300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="Q43" s="3">
         <v>2600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="R43" s="3">
         <v>2200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="S43" s="3">
         <v>1900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="T43" s="3">
         <v>1200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="U43" s="3">
         <v>500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="V43" s="3">
         <v>400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="W43" s="3">
         <v>200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="X43" s="3">
         <v>100</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F44" s="3">
+        <v>6400</v>
+      </c>
+      <c r="G44" s="3">
         <v>5800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="H44" s="3">
         <v>5800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="I44" s="3">
         <v>6500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="J44" s="3">
         <v>5600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="K44" s="3">
         <v>4000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="L44" s="3">
         <v>3000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="M44" s="3">
         <v>2000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="N44" s="3">
         <v>1900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="O44" s="3">
         <v>1600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="P44" s="3">
         <v>2300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="Q44" s="3">
         <v>2800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="R44" s="3">
         <v>3600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="S44" s="3">
         <v>2700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="T44" s="3">
         <v>2000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="U44" s="3">
         <v>2100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="V44" s="3">
         <v>2300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="W44" s="3">
         <v>2200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="X44" s="3">
         <v>2000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="Y44" s="3">
         <v>1300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Z44" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K45" s="3">
         <v>800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="L45" s="3">
+        <v>600</v>
+      </c>
+      <c r="M45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="N45" s="3">
+        <v>700</v>
+      </c>
+      <c r="O45" s="3">
         <v>900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="P45" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q45" s="3">
         <v>800</v>
       </c>
-      <c r="I45" s="3">
-        <v>600</v>
-      </c>
-      <c r="J45" s="3">
-        <v>700</v>
-      </c>
-      <c r="K45" s="3">
-        <v>700</v>
-      </c>
-      <c r="L45" s="3">
-        <v>900</v>
-      </c>
-      <c r="M45" s="3">
-        <v>500</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="R45" s="3">
         <v>800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="S45" s="3">
         <v>800</v>
-      </c>
-      <c r="P45" s="3">
-        <v>800</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>300</v>
-      </c>
-      <c r="R45" s="3">
-        <v>300</v>
-      </c>
-      <c r="S45" s="3">
-        <v>300</v>
       </c>
       <c r="T45" s="3">
         <v>300</v>
       </c>
       <c r="U45" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="V45" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W45" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z45" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F46" s="3">
+        <v>17700</v>
+      </c>
+      <c r="G46" s="3">
         <v>21200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="H46" s="3">
         <v>25800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
         <v>27400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="J46" s="3">
         <v>23600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="K46" s="3">
         <v>26900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="L46" s="3">
         <v>29500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3">
         <v>32600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>36800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="O46" s="3">
         <v>41200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="P46" s="3">
         <v>45900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="Q46" s="3">
         <v>49300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="R46" s="3">
         <v>43600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="S46" s="3">
         <v>46900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="T46" s="3">
         <v>48500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="U46" s="3">
         <v>38200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="V46" s="3">
         <v>18500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="W46" s="3">
         <v>19700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="X46" s="3">
         <v>21400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="Y46" s="3">
         <v>22900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Z46" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3026,55 +3341,64 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F48" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G48" s="3">
         <v>2800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="H48" s="3">
         <v>700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
         <v>800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="J48" s="3">
         <v>900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="K48" s="3">
         <v>1000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="L48" s="3">
         <v>1100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
         <v>1200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="N48" s="3">
         <v>1300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="O48" s="3">
         <v>1000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="P48" s="3">
         <v>1000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="Q48" s="3">
         <v>600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="R48" s="3">
         <v>600</v>
-      </c>
-      <c r="P48" s="3">
-        <v>500</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>500</v>
-      </c>
-      <c r="R48" s="3">
-        <v>500</v>
       </c>
       <c r="S48" s="3">
         <v>500</v>
@@ -3086,78 +3410,96 @@
         <v>500</v>
       </c>
       <c r="V48" s="3">
+        <v>500</v>
+      </c>
+      <c r="W48" s="3">
+        <v>500</v>
+      </c>
+      <c r="X48" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y48" s="3">
         <v>400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Z48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F49" s="3">
+        <v>4200</v>
+      </c>
+      <c r="G49" s="3">
         <v>4300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="H49" s="3">
         <v>4900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="I49" s="3">
         <v>2600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="J49" s="3">
         <v>2600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="K49" s="3">
         <v>2600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="L49" s="3">
         <v>1900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="M49" s="3">
         <v>1900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="N49" s="3">
         <v>2000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="O49" s="3">
         <v>2000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="P49" s="3">
         <v>1800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="Q49" s="3">
         <v>1400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="R49" s="3">
         <v>1400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="S49" s="3">
         <v>1400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="T49" s="3">
         <v>300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="U49" s="3">
         <v>300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="V49" s="3">
         <v>300</v>
-      </c>
-      <c r="T49" s="3">
-        <v>200</v>
-      </c>
-      <c r="U49" s="3">
-        <v>200</v>
-      </c>
-      <c r="V49" s="3">
-        <v>200</v>
       </c>
       <c r="W49" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y49" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z49" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3563,17 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,35 +3637,44 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E52" s="3">
         <v>200</v>
       </c>
       <c r="F52" s="3">
+        <v>200</v>
+      </c>
+      <c r="G52" s="3">
+        <v>300</v>
+      </c>
+      <c r="H52" s="3">
+        <v>200</v>
+      </c>
+      <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -3351,8 +3711,17 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,73 +3785,91 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>21800</v>
+      </c>
+      <c r="F54" s="3">
+        <v>24800</v>
+      </c>
+      <c r="G54" s="3">
         <v>28500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>31700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
         <v>30900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="J54" s="3">
         <v>27200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="K54" s="3">
         <v>30600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="L54" s="3">
         <v>32500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>35800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>40100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>44200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>48700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="Q54" s="3">
         <v>51300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="R54" s="3">
         <v>45600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="S54" s="3">
         <v>48800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="T54" s="3">
         <v>49400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="U54" s="3">
         <v>39000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="V54" s="3">
         <v>19300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="W54" s="3">
         <v>20400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="X54" s="3">
         <v>22100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="Y54" s="3">
         <v>23500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Z54" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3893,11 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,96 +3921,108 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H57" s="3">
         <v>1500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="I57" s="3">
         <v>1900</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>900</v>
       </c>
       <c r="J57" s="3">
         <v>1400</v>
       </c>
       <c r="K57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L57" s="3">
+        <v>900</v>
+      </c>
+      <c r="M57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N57" s="3">
         <v>1700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="O57" s="3">
         <v>1800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="P57" s="3">
         <v>1500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="Q57" s="3">
         <v>1300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="R57" s="3">
         <v>2400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="S57" s="3">
         <v>1200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="T57" s="3">
         <v>800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="U57" s="3">
         <v>800</v>
-      </c>
-      <c r="S57" s="3">
-        <v>400</v>
-      </c>
-      <c r="T57" s="3">
-        <v>400</v>
-      </c>
-      <c r="U57" s="3">
-        <v>700</v>
       </c>
       <c r="V57" s="3">
         <v>400</v>
       </c>
       <c r="W57" s="3">
+        <v>400</v>
+      </c>
+      <c r="X57" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z57" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3637,185 +4039,212 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>10</v>
+      <c r="P58" s="3">
+        <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T58" s="3">
         <v>200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="U58" s="3">
         <v>200</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>10</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z58" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>22400</v>
+        <v>8800</v>
       </c>
       <c r="E59" s="3">
-        <v>9300</v>
+        <v>14200</v>
       </c>
       <c r="F59" s="3">
-        <v>8900</v>
+        <v>16400</v>
       </c>
       <c r="G59" s="3">
-        <v>2000</v>
+        <v>21500</v>
       </c>
       <c r="H59" s="3">
+        <v>8400</v>
+      </c>
+      <c r="I59" s="3">
+        <v>8000</v>
+      </c>
+      <c r="J59" s="3">
+        <v>600</v>
+      </c>
+      <c r="K59" s="3">
         <v>1700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="L59" s="3">
         <v>1200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3">
         <v>1200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="N59" s="3">
         <v>1000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="O59" s="3">
         <v>1100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="P59" s="3">
         <v>1600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="Q59" s="3">
         <v>1300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="R59" s="3">
         <v>1000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="S59" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>700</v>
-      </c>
-      <c r="R59" s="3">
-        <v>600</v>
-      </c>
-      <c r="S59" s="3">
-        <v>600</v>
       </c>
       <c r="T59" s="3">
         <v>700</v>
       </c>
       <c r="U59" s="3">
+        <v>600</v>
+      </c>
+      <c r="V59" s="3">
+        <v>600</v>
+      </c>
+      <c r="W59" s="3">
+        <v>700</v>
+      </c>
+      <c r="X59" s="3">
         <v>500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="Y59" s="3">
         <v>300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Z59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>16200</v>
+      </c>
+      <c r="F60" s="3">
+        <v>18500</v>
+      </c>
+      <c r="G60" s="3">
         <v>23500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="H60" s="3">
         <v>10800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
         <v>10800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="J60" s="3">
         <v>3400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="K60" s="3">
         <v>3200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="L60" s="3">
         <v>2200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3">
         <v>2600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="N60" s="3">
         <v>2800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="O60" s="3">
         <v>2900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="P60" s="3">
         <v>3100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="Q60" s="3">
         <v>2600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="R60" s="3">
         <v>3400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="S60" s="3">
         <v>2300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="T60" s="3">
         <v>1700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="U60" s="3">
         <v>1600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="V60" s="3">
         <v>1000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="W60" s="3">
         <v>1100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="X60" s="3">
         <v>1300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="Y60" s="3">
         <v>800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Z60" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3836,63 +4265,72 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="U61" s="3">
         <v>300</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>1800</v>
-      </c>
-      <c r="E62" s="3">
-        <v>300</v>
-      </c>
-      <c r="F62" s="3">
-        <v>300</v>
-      </c>
-      <c r="G62" s="3">
-        <v>300</v>
-      </c>
-      <c r="H62" s="3">
-        <v>400</v>
-      </c>
-      <c r="I62" s="3">
-        <v>400</v>
-      </c>
-      <c r="J62" s="3">
-        <v>400</v>
+      <c r="D62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K62" s="3">
         <v>400</v>
       </c>
       <c r="L62" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="M62" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="N62" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="O62" s="3">
         <v>100</v>
@@ -3901,7 +4339,7 @@
         <v>100</v>
       </c>
       <c r="Q62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R62" s="3">
         <v>100</v>
@@ -3910,19 +4348,28 @@
         <v>100</v>
       </c>
       <c r="T62" s="3">
+        <v>100</v>
+      </c>
+      <c r="U62" s="3">
+        <v>100</v>
+      </c>
+      <c r="V62" s="3">
+        <v>100</v>
+      </c>
+      <c r="W62" s="3">
         <v>200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="X62" s="3">
         <v>200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="Y62" s="3">
         <v>200</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4433,17 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4507,17 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,73 +4581,91 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>17900</v>
+      </c>
+      <c r="F66" s="3">
+        <v>20300</v>
+      </c>
+      <c r="G66" s="3">
         <v>25300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="H66" s="3">
         <v>11100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
         <v>11100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="J66" s="3">
         <v>3700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="K66" s="3">
         <v>3500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="L66" s="3">
         <v>2600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
         <v>3000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="N66" s="3">
         <v>3200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="O66" s="3">
         <v>3000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="P66" s="3">
         <v>3200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="Q66" s="3">
         <v>2600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="R66" s="3">
         <v>3500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="S66" s="3">
         <v>2400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="T66" s="3">
         <v>2000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="U66" s="3">
         <v>1900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="V66" s="3">
         <v>1100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="W66" s="3">
         <v>1200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="X66" s="3">
         <v>1400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="Y66" s="3">
         <v>1000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Z66" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4689,11 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4757,17 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,25 +4831,34 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3">
         <v>2000</v>
       </c>
-      <c r="E70" s="3">
-        <v>0</v>
-      </c>
-      <c r="F70" s="3">
-        <v>0</v>
-      </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I70" s="3">
         <v>0</v>
@@ -4401,8 +4905,17 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,73 +4979,91 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-97300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-99000</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-98100</v>
+      </c>
+      <c r="G72" s="3">
         <v>-98000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="H72" s="3">
         <v>-79400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="I72" s="3">
         <v>-76400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="J72" s="3">
         <v>-71400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="K72" s="3">
         <v>-67400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="L72" s="3">
         <v>-63800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>-60000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="N72" s="3">
         <v>-55200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="O72" s="3">
         <v>-49800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="P72" s="3">
         <v>-44500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="Q72" s="3">
         <v>-38500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="R72" s="3">
         <v>-30700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="S72" s="3">
         <v>-25300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="T72" s="3">
         <v>-21800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="U72" s="3">
         <v>-17900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="V72" s="3">
         <v>-15100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="W72" s="3">
         <v>-12700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="X72" s="3">
         <v>-10200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="Y72" s="3">
         <v>-7800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Z72" s="3">
         <v>-5900</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +5127,17 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +5201,17 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,73 +5275,91 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F76" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G76" s="3">
         <v>1100</v>
       </c>
-      <c r="E76" s="3">
-        <v>20600</v>
-      </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
+        <v>18500</v>
+      </c>
+      <c r="I76" s="3">
         <v>19800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="J76" s="3">
         <v>23600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="K76" s="3">
         <v>27100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="L76" s="3">
         <v>30000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
         <v>32900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>36900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="O76" s="3">
         <v>41300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="P76" s="3">
         <v>45500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="Q76" s="3">
         <v>48800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="R76" s="3">
         <v>42100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="S76" s="3">
         <v>46400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="T76" s="3">
         <v>47400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="U76" s="3">
         <v>37100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="V76" s="3">
         <v>18100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="W76" s="3">
         <v>19200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="X76" s="3">
         <v>20700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="Y76" s="3">
         <v>22500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Z76" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5423,170 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-18800</v>
+        <v>2000</v>
       </c>
       <c r="E81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F81" s="3">
+        <v>100</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="H81" s="3">
         <v>-2800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="I81" s="3">
         <v>-5000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="J81" s="3">
         <v>-4000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="K81" s="3">
         <v>-3500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="L81" s="3">
         <v>-3900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="M81" s="3">
         <v>-4800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="N81" s="3">
         <v>-5400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="O81" s="3">
         <v>-5200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="P81" s="3">
         <v>-6000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="Q81" s="3">
         <v>-7800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="R81" s="3">
         <v>-5400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="S81" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="T81" s="3">
         <v>-3900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="U81" s="3">
         <v>-2800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="V81" s="3">
         <v>-2300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="W81" s="3">
         <v>-2500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="X81" s="3">
         <v>-2400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="Y81" s="3">
         <v>-1900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Z81" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,43 +5610,46 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>200</v>
+      </c>
+      <c r="F83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>300</v>
       </c>
-      <c r="F83" s="3">
-        <v>200</v>
-      </c>
-      <c r="G83" s="3">
-        <v>200</v>
-      </c>
       <c r="H83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>200</v>
       </c>
       <c r="L83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O83" s="3">
         <v>100</v>
@@ -5061,13 +5658,13 @@
         <v>100</v>
       </c>
       <c r="Q83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -5081,8 +5678,17 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5752,17 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5826,17 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5900,17 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5974,17 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,73 +6048,91 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="G89" s="3">
         <v>-3800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="H89" s="3">
         <v>-12100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="I89" s="3">
         <v>2300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="J89" s="3">
         <v>-3100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="K89" s="3">
         <v>-3600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="L89" s="3">
         <v>-4800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="M89" s="3">
         <v>-1400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="N89" s="3">
         <v>-4900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="O89" s="3">
         <v>-4500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="P89" s="3">
         <v>-3500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="Q89" s="3">
         <v>-5800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="R89" s="3">
         <v>-4400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="S89" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="T89" s="3">
         <v>-3800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="U89" s="3">
         <v>-1700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="V89" s="3">
         <v>-2200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="W89" s="3">
         <v>-2700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="X89" s="3">
         <v>-2100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="Y89" s="3">
         <v>-2100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Z89" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,55 +6156,58 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
       </c>
       <c r="H91" s="3">
-        <v>-800</v>
+        <v>-100</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-400</v>
-      </c>
       <c r="M91" s="3">
-        <v>-1000</v>
+        <v>-100</v>
       </c>
       <c r="N91" s="3">
         <v>-200</v>
       </c>
       <c r="O91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-100</v>
-      </c>
       <c r="R91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -5553,16 +6216,25 @@
         <v>-100</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +6298,17 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,61 +6372,70 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F94" s="3">
         <v>2400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H94" s="3">
         <v>-4400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="J94" s="3">
         <v>7200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="K94" s="3">
         <v>5100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="L94" s="3">
         <v>5000</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>4900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="O94" s="3">
         <v>-400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="P94" s="3">
         <v>-1000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="Q94" s="3">
         <v>4700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="R94" s="3">
         <v>-10200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="S94" s="3">
         <v>-800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="T94" s="3">
         <v>-25100</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="S94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-100</v>
       </c>
       <c r="U94" s="3">
         <v>-100</v>
@@ -5756,8 +6446,17 @@
       <c r="W94" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,31 +6480,34 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5846,8 +6548,17 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6622,17 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6696,17 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,96 +6770,114 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F100" s="3">
+        <v>500</v>
+      </c>
+      <c r="G100" s="3">
         <v>400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="H100" s="3">
         <v>9800</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="I100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>1300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="Q100" s="3">
         <v>12100</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>1800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="T100" s="3">
         <v>13700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="U100" s="3">
         <v>21600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="V100" s="3">
         <v>800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="W100" s="3">
         <v>500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="X100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6171,69 +6918,87 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="G102" s="3">
         <v>-1000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="H102" s="3">
         <v>-6800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="I102" s="3">
         <v>2200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="J102" s="3">
         <v>4200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="K102" s="3">
         <v>1500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="L102" s="3">
         <v>200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="M102" s="3">
         <v>-1400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="N102" s="3">
         <v>100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="O102" s="3">
         <v>-4900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="P102" s="3">
         <v>-3200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="Q102" s="3">
         <v>11100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="R102" s="3">
         <v>-14600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="S102" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="T102" s="3">
         <v>-15300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="U102" s="3">
         <v>19900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="V102" s="3">
         <v>-1500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="W102" s="3">
         <v>-2300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="X102" s="3">
         <v>-2100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="Y102" s="3">
         <v>10700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Z102" s="3">
         <v>-1700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WRAP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WRAP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
   <si>
     <t>WRAP</t>
   </si>
@@ -656,340 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>900</v>
+      </c>
+      <c r="F8" s="3">
         <v>600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>3600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>3600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>500</v>
+      </c>
+      <c r="F9" s="3">
         <v>400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>2000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>200</v>
       </c>
-      <c r="Y9" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>400</v>
+      </c>
+      <c r="F10" s="3">
         <v>200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>-300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>2200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>500</v>
-      </c>
-      <c r="N10" s="3">
-        <v>700</v>
-      </c>
-      <c r="O10" s="3">
-        <v>700</v>
       </c>
       <c r="P10" s="3">
         <v>700</v>
       </c>
       <c r="Q10" s="3">
+        <v>700</v>
+      </c>
+      <c r="R10" s="3">
+        <v>700</v>
+      </c>
+      <c r="S10" s="3">
         <v>-100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>500</v>
-      </c>
-      <c r="T10" s="3">
-        <v>300</v>
-      </c>
-      <c r="U10" s="3">
-        <v>200</v>
       </c>
       <c r="V10" s="3">
         <v>300</v>
       </c>
       <c r="W10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X10" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Y10" s="3">
         <v>100</v>
       </c>
       <c r="Z10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1016,82 +1041,90 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>400</v>
+      </c>
+      <c r="E12" s="3">
+        <v>400</v>
+      </c>
+      <c r="F12" s="3">
         <v>500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>2100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>900</v>
-      </c>
-      <c r="U12" s="3">
-        <v>600</v>
-      </c>
-      <c r="V12" s="3">
-        <v>500</v>
       </c>
       <c r="W12" s="3">
         <v>600</v>
       </c>
       <c r="X12" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="Y12" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="Z12" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1164,28 +1197,34 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>10</v>
+      <c r="E14" s="3">
+        <v>1600</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="3">
-        <v>-200</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>10</v>
+      <c r="I14" s="3">
+        <v>1700</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>10</v>
@@ -1202,27 +1241,27 @@
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>10</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U14" s="3">
         <v>-400</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1238,8 +1277,14 @@
       <c r="Z14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1253,23 +1298,23 @@
         <v>200</v>
       </c>
       <c r="G15" s="3">
+        <v>200</v>
+      </c>
+      <c r="H15" s="3">
+        <v>200</v>
+      </c>
+      <c r="I15" s="3">
         <v>100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1312,8 +1357,14 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1388,170 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F17" s="3">
         <v>4200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>4700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>5600</v>
       </c>
-      <c r="G17" s="3">
-        <v>7400</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>5500</v>
+      </c>
+      <c r="J17" s="3">
         <v>6400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>6300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>5000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>7200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>5600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>5900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>7000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>7700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>7800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>9700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>7000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>5000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>4900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>3700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>3100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>2900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>2800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>2000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-3200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-4100</v>
       </c>
-      <c r="G18" s="3">
-        <v>-6800</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="J18" s="3">
         <v>-2800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-5100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-4300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-3600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-4700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-5400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-5300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-7800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-5500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-3600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-3900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-2900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-2400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-2600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,156 +1578,170 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-5600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-2700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-4200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>11700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="F21" s="3">
         <v>2200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-18400</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="J21" s="3">
         <v>-2600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-4900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-4100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-3300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-3700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-4600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-5200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-5100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-7700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-5300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-3500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-3800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-2800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-2300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-2500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1696,11 +1775,11 @@
       <c r="M22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1720,8 +1799,8 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>10</v>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -1729,88 +1808,100 @@
       <c r="X22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>10</v>
+      <c r="Y22" s="3">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="F23" s="3">
         <v>2000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-18400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-2800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-5000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-4000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-3500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-3900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-4800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-5400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-5200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-7800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-5400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-3600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-3900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-2800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-2300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-2500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1835,11 +1926,11 @@
       <c r="J24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1883,8 +1974,14 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2054,174 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="F26" s="3">
         <v>2000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-18400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-5000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-4000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-3500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-3900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-4800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-5400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-5200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-7800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-5400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-3600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-3900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-2800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-2300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-2500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="F27" s="3">
         <v>1700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-18600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-3000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-5000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-4000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-3500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-3900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-4800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-5400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-5200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-7800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-5400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-3600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-3900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-2800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-2300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-2500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2294,14 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2374,14 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2454,14 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,156 +2534,174 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F32" s="3">
         <v>5600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>2700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>4200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-11700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="F33" s="3">
         <v>2000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-18400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-5000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-4000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-3500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-3900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-4800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-5400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-5200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-7800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-5400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-3600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-3900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-2800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-2300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-2500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2774,179 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="F35" s="3">
         <v>2000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-18400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-5000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-4000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-3500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-3900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-4800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-5400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-5200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-7800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-5400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-3600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-3900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-2800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-2300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-2500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2973,10 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,82 +3003,90 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F41" s="3">
         <v>4900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>11700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>9500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>5300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>3600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>5000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>4900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>9900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>13100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>2000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>16600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>20100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>35400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>15500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>17000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>19300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>21400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2915,59 +3094,59 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>2500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>5000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>7500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>10000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>6500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>6500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>13900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>19900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>24900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>25000</v>
-      </c>
-      <c r="O42" s="3">
-        <v>30000</v>
-      </c>
-      <c r="P42" s="3">
-        <v>30000</v>
       </c>
       <c r="Q42" s="3">
         <v>30000</v>
       </c>
       <c r="R42" s="3">
+        <v>30000</v>
+      </c>
+      <c r="S42" s="3">
+        <v>30000</v>
+      </c>
+      <c r="T42" s="3">
         <v>35000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>25000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>25000</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="V42" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>10</v>
       </c>
@@ -2980,156 +3159,174 @@
       <c r="Z42" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB42" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>500</v>
+      </c>
+      <c r="F43" s="3">
         <v>800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>3300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>3000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>4300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>4200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>3300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>2600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>2200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>200</v>
-      </c>
-      <c r="X43" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>0</v>
       </c>
       <c r="Z43" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F44" s="3">
         <v>6300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>6500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>6400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>5800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>5800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>6500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>5600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>4000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>3000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>2000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>2300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>2800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>3600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>2700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>2000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>2100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>2300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>2200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>2000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>1300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3154,38 +3351,38 @@
       <c r="J45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M45" s="3">
         <v>800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>500</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>800</v>
-      </c>
-      <c r="R45" s="3">
-        <v>800</v>
       </c>
       <c r="S45" s="3">
         <v>800</v>
       </c>
       <c r="T45" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="U45" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="V45" s="3">
         <v>300</v>
@@ -3194,90 +3391,102 @@
         <v>300</v>
       </c>
       <c r="X45" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z45" s="3">
         <v>100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>10500</v>
+      </c>
+      <c r="F46" s="3">
         <v>12200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>15000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>17700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>21200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>25800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>27400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>23600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>26900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>29500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>32600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>36800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>41200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>45900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>49300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>43600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>46900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>48500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>38200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>18500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>19700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>21400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>22900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3302,11 +3511,11 @@
       <c r="J47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3350,61 +3559,67 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F48" s="3">
         <v>2200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>600</v>
-      </c>
-      <c r="S48" s="3">
-        <v>500</v>
-      </c>
-      <c r="T48" s="3">
-        <v>500</v>
       </c>
       <c r="U48" s="3">
         <v>500</v>
@@ -3419,78 +3634,84 @@
         <v>500</v>
       </c>
       <c r="Y48" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z48" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA48" s="3">
         <v>400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F49" s="3">
         <v>4100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>4100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>4200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>4300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>4900</v>
-      </c>
-      <c r="I49" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J49" s="3">
-        <v>2600</v>
       </c>
       <c r="K49" s="3">
         <v>2600</v>
       </c>
       <c r="L49" s="3">
+        <v>2600</v>
+      </c>
+      <c r="M49" s="3">
+        <v>2600</v>
+      </c>
+      <c r="N49" s="3">
         <v>1900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>2000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>2000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>1800</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>1400</v>
-      </c>
-      <c r="R49" s="3">
-        <v>1400</v>
       </c>
       <c r="S49" s="3">
         <v>1400</v>
       </c>
       <c r="T49" s="3">
-        <v>300</v>
+        <v>1400</v>
       </c>
       <c r="U49" s="3">
-        <v>300</v>
+        <v>1400</v>
       </c>
       <c r="V49" s="3">
         <v>300</v>
       </c>
       <c r="W49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Y49" s="3">
         <v>200</v>
@@ -3498,8 +3719,14 @@
       <c r="Z49" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB49" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3799,14 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,13 +3879,19 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
         <v>200</v>
@@ -3661,25 +3900,25 @@
         <v>200</v>
       </c>
       <c r="G52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H52" s="3">
         <v>200</v>
       </c>
       <c r="I52" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K52" s="3">
         <v>100</v>
       </c>
       <c r="L52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -3720,8 +3959,14 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,82 +4039,94 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>15100</v>
+      </c>
+      <c r="F54" s="3">
         <v>18800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>21800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>24800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>28500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>31700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>30900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>27200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>30600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>32500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>35800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>40100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>44200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>48700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>51300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>45600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>48800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>49400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>39000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>19300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>20400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>22100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>23500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4153,10 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,73 +4183,75 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>600</v>
+      </c>
+      <c r="F57" s="3">
         <v>1300</v>
-      </c>
-      <c r="E57" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F57" s="3">
-        <v>1100</v>
       </c>
       <c r="G57" s="3">
         <v>1100</v>
       </c>
       <c r="H57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J57" s="3">
         <v>1500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1400</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1400</v>
-      </c>
-      <c r="L57" s="3">
-        <v>900</v>
       </c>
       <c r="M57" s="3">
         <v>1400</v>
       </c>
       <c r="N57" s="3">
+        <v>900</v>
+      </c>
+      <c r="O57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P57" s="3">
         <v>1700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>2400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>400</v>
-      </c>
-      <c r="W57" s="3">
-        <v>400</v>
-      </c>
-      <c r="X57" s="3">
-        <v>700</v>
       </c>
       <c r="Y57" s="3">
         <v>400</v>
@@ -3998,37 +4259,43 @@
       <c r="Z57" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB57" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E58" s="3">
         <v>600</v>
       </c>
       <c r="F58" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="G58" s="3">
         <v>600</v>
       </c>
       <c r="H58" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="I58" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="J58" s="3">
         <v>100</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -4048,21 +4315,21 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>10</v>
+      <c r="S58" s="3">
+        <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V58" s="3">
         <v>200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>200</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W58" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>10</v>
       </c>
@@ -4072,161 +4339,179 @@
       <c r="Z58" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB58" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>11200</v>
+      </c>
+      <c r="F59" s="3">
         <v>8800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>14200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>16400</v>
       </c>
-      <c r="G59" s="3">
-        <v>21500</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>21300</v>
+      </c>
+      <c r="J59" s="3">
         <v>8400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>8000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>13200</v>
+      </c>
+      <c r="F60" s="3">
         <v>10700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>16200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>18500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>23500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>10800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>10800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>3100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>3400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>2300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="E61" s="3">
         <v>1600</v>
@@ -4235,23 +4520,23 @@
         <v>1700</v>
       </c>
       <c r="G61" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H61" s="3">
         <v>1700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J61" s="3">
         <v>100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>200</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4274,17 +4559,17 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>300</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4294,8 +4579,14 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4320,11 +4611,11 @@
       <c r="J62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K62" s="3">
-        <v>400</v>
-      </c>
-      <c r="L62" s="3">
-        <v>400</v>
+      <c r="K62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M62" s="3">
         <v>400</v>
@@ -4333,19 +4624,19 @@
         <v>400</v>
       </c>
       <c r="O62" s="3">
+        <v>400</v>
+      </c>
+      <c r="P62" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q62" s="3">
         <v>100</v>
-      </c>
-      <c r="P62" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>0</v>
       </c>
       <c r="R62" s="3">
         <v>100</v>
       </c>
       <c r="S62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T62" s="3">
         <v>100</v>
@@ -4357,19 +4648,25 @@
         <v>100</v>
       </c>
       <c r="W62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y62" s="3">
         <v>200</v>
       </c>
       <c r="Z62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AA62" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4739,14 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4819,14 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,43 +4899,49 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>14900</v>
+      </c>
+      <c r="F66" s="3">
         <v>12400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>17900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>20300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>25300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>11100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>11100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>2600</v>
-      </c>
-      <c r="M66" s="3">
-        <v>3000</v>
-      </c>
-      <c r="N66" s="3">
-        <v>3200</v>
       </c>
       <c r="O66" s="3">
         <v>3000</v>
@@ -4635,37 +4950,43 @@
         <v>3200</v>
       </c>
       <c r="Q66" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R66" s="3">
+        <v>3200</v>
+      </c>
+      <c r="S66" s="3">
         <v>2600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>3500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>2400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>2000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +5013,10 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +5089,14 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5169,14 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4852,10 +5187,10 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="G70" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="H70" s="3">
         <v>2000</v>
@@ -4864,7 +5199,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -4914,8 +5249,14 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,82 +5329,94 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-105100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-105100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-97300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-99000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-98100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-98000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-79400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-76400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-71400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-67400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-63800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-60000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-55200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-49800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-44500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-38500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-30700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-25300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-21800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-17900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-15100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-12700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-7800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-5900</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5489,14 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5569,14 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,82 +5649,94 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>300</v>
+      </c>
+      <c r="F76" s="3">
         <v>6400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2500</v>
       </c>
-      <c r="G76" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J76" s="3">
         <v>18500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>19800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>23600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>27100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>30000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>32900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>36900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>41300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>45500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>48800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>42100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>46400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>47400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>37100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>18100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>19200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>20700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>22500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5809,179 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="F81" s="3">
         <v>2000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-18400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-5000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-4000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-3500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-3900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-4800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-5400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-5200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-7800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-5400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-3600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-3900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-2800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-2300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-2500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,37 +6008,39 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>200</v>
       </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
       </c>
       <c r="K83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M83" s="3">
         <v>200</v>
@@ -5652,10 +6049,10 @@
         <v>200</v>
       </c>
       <c r="O83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q83" s="3">
         <v>100</v>
@@ -5667,10 +6064,10 @@
         <v>100</v>
       </c>
       <c r="T83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -5687,8 +6084,14 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +6164,14 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6244,14 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6324,14 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6404,14 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,82 +6484,94 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F89" s="3">
         <v>300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-3500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-3700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-3800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-12100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>2300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-3100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-3600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-4800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-4900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-4500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-5800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-4400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-4500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-3800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-1700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-2200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-2700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,8 +6598,10 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6174,67 +6615,73 @@
         <v>0</v>
       </c>
       <c r="G91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y91" s="3">
         <v>-100</v>
       </c>
       <c r="Z91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6754,14 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,67 +6834,73 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F94" s="3">
         <v>2500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>2500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>2400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>2400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-4400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>7200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>5100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>5000</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>4900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>4700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-10200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-25100</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="V94" s="3">
-        <v>-100</v>
       </c>
       <c r="W94" s="3">
         <v>-100</v>
@@ -6455,8 +6914,14 @@
       <c r="Z94" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,37 +6948,39 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" s="3">
         <v>100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>100</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="J96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6557,8 +7024,14 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +7104,14 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +7184,14 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,82 +7264,94 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>9800</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>1300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>12100</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>1800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>13700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>21600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>100</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z100" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6879,11 +7376,11 @@
       <c r="J101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6927,78 +7424,90 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F102" s="3">
         <v>2800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-6800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>2200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>4200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-4900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>11100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-14600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-3500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-15300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>19900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-1500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-2300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>10700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-1700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WRAP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WRAP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
   <si>
     <t>WRAP</t>
   </si>
@@ -656,326 +656,336 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E8" s="3">
         <v>800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>700</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>300</v>
       </c>
       <c r="Z8" s="3">
         <v>300</v>
       </c>
       <c r="AA8" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AB8" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>500</v>
+      </c>
+      <c r="E9" s="3">
         <v>200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>400</v>
-      </c>
-      <c r="G9" s="3">
-        <v>600</v>
       </c>
       <c r="H9" s="3">
         <v>600</v>
       </c>
       <c r="I9" s="3">
+        <v>600</v>
+      </c>
+      <c r="J9" s="3">
         <v>900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2000</v>
-      </c>
-      <c r="T9" s="3">
-        <v>900</v>
       </c>
       <c r="U9" s="3">
         <v>900</v>
       </c>
       <c r="V9" s="3">
+        <v>900</v>
+      </c>
+      <c r="W9" s="3">
         <v>700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>400</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>200</v>
       </c>
       <c r="Z9" s="3">
         <v>200</v>
       </c>
       <c r="AA9" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>500</v>
+      </c>
+      <c r="E10" s="3">
         <v>600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>500</v>
-      </c>
-      <c r="P10" s="3">
-        <v>700</v>
       </c>
       <c r="Q10" s="3">
         <v>700</v>
@@ -984,25 +994,25 @@
         <v>700</v>
       </c>
       <c r="S10" s="3">
+        <v>700</v>
+      </c>
+      <c r="T10" s="3">
         <v>-100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>300</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>100</v>
       </c>
       <c r="Z10" s="3">
         <v>100</v>
@@ -1011,10 +1021,13 @@
         <v>100</v>
       </c>
       <c r="AB10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,88 +1056,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E12" s="3">
         <v>400</v>
       </c>
       <c r="F12" s="3">
+        <v>400</v>
+      </c>
+      <c r="G12" s="3">
         <v>500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>800</v>
-      </c>
-      <c r="I12" s="3">
-        <v>600</v>
       </c>
       <c r="J12" s="3">
         <v>600</v>
       </c>
       <c r="K12" s="3">
+        <v>600</v>
+      </c>
+      <c r="L12" s="3">
         <v>1000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1200</v>
-      </c>
-      <c r="O12" s="3">
-        <v>1500</v>
       </c>
       <c r="P12" s="3">
         <v>1500</v>
       </c>
       <c r="Q12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R12" s="3">
         <v>1900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1203,32 +1220,35 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="3">
         <v>1600</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="3">
         <v>1700</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1247,11 +1267,11 @@
       <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>10</v>
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>10</v>
@@ -1259,12 +1279,12 @@
       <c r="T14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V14" s="3">
         <v>-400</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1283,13 +1303,16 @@
       <c r="AB14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
         <v>200</v>
@@ -1304,19 +1327,19 @@
         <v>200</v>
       </c>
       <c r="I15" s="3">
+        <v>200</v>
+      </c>
+      <c r="J15" s="3">
         <v>100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>300</v>
-      </c>
-      <c r="K15" s="3">
-        <v>200</v>
       </c>
       <c r="L15" s="3">
         <v>200</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1363,8 +1386,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E17" s="3">
         <v>4700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-7800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,44 +1613,45 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>11700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1625,123 +1659,129 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E21" s="3">
         <v>300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-5800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-16500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-4600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-5100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-5900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-7700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1781,8 +1821,8 @@
       <c r="O22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1805,14 +1845,14 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="3" t="s">
-        <v>10</v>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>10</v>
@@ -1820,88 +1860,94 @@
       <c r="AB22" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E23" s="3">
         <v>100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-18400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-7800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1932,8 +1978,8 @@
       <c r="L24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1980,8 +2026,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E26" s="3">
         <v>100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-7600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-18400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-7800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-7800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-18600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,44 +2607,47 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E32" s="3">
         <v>4000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-11700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2585,123 +2655,129 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E33" s="3">
         <v>100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-7600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-18400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-6000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E35" s="3">
         <v>100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-7600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-18400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-6000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,88 +3091,92 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E41" s="3">
         <v>6200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>13100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>16600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>20100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>35400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>15500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>17000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>19300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>21400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3100,37 +3190,37 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>2500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>7500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>10000</v>
-      </c>
-      <c r="K42" s="3">
-        <v>6500</v>
       </c>
       <c r="L42" s="3">
         <v>6500</v>
       </c>
       <c r="M42" s="3">
+        <v>6500</v>
+      </c>
+      <c r="N42" s="3">
         <v>13900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>19900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>24900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>25000</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>30000</v>
       </c>
       <c r="R42" s="3">
         <v>30000</v>
@@ -3139,16 +3229,16 @@
         <v>30000</v>
       </c>
       <c r="T42" s="3">
+        <v>30000</v>
+      </c>
+      <c r="U42" s="3">
         <v>35000</v>
-      </c>
-      <c r="U42" s="3">
-        <v>25000</v>
       </c>
       <c r="V42" s="3">
         <v>25000</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>10</v>
+      <c r="W42" s="3">
+        <v>25000</v>
       </c>
       <c r="X42" s="3" t="s">
         <v>10</v>
@@ -3165,168 +3255,177 @@
       <c r="AB42" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>900</v>
+      </c>
+      <c r="E43" s="3">
         <v>700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>100</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
-      </c>
       <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E44" s="3">
         <v>6100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6400</v>
-      </c>
-      <c r="I44" s="3">
-        <v>5800</v>
       </c>
       <c r="J44" s="3">
         <v>5800</v>
       </c>
       <c r="K44" s="3">
+        <v>5800</v>
+      </c>
+      <c r="L44" s="3">
         <v>6500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3357,26 +3456,26 @@
       <c r="L45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N45" s="3">
         <v>800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>600</v>
-      </c>
-      <c r="O45" s="3">
-        <v>700</v>
       </c>
       <c r="P45" s="3">
         <v>700</v>
       </c>
       <c r="Q45" s="3">
+        <v>700</v>
+      </c>
+      <c r="R45" s="3">
         <v>900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>500</v>
-      </c>
-      <c r="S45" s="3">
-        <v>800</v>
       </c>
       <c r="T45" s="3">
         <v>800</v>
@@ -3385,7 +3484,7 @@
         <v>800</v>
       </c>
       <c r="V45" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="W45" s="3">
         <v>300</v>
@@ -3397,96 +3496,102 @@
         <v>300</v>
       </c>
       <c r="Z45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA45" s="3">
         <v>100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E46" s="3">
         <v>13500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>17700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>25800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>27400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>23600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>26900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>29500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>32600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>36800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>41200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>45900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>49300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>43600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>46900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>48500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>38200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>18500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>19700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>21400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>22900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3517,8 +3622,8 @@
       <c r="L47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3565,64 +3670,67 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E48" s="3">
         <v>2000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1300</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>1000</v>
       </c>
       <c r="R48" s="3">
         <v>1000</v>
       </c>
       <c r="S48" s="3">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="T48" s="3">
         <v>600</v>
       </c>
       <c r="U48" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="V48" s="3">
         <v>500</v>
@@ -3640,13 +3748,16 @@
         <v>500</v>
       </c>
       <c r="AA48" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB48" s="3">
         <v>400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3654,25 +3765,25 @@
         <v>2300</v>
       </c>
       <c r="E49" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F49" s="3">
         <v>2400</v>
-      </c>
-      <c r="F49" s="3">
-        <v>4100</v>
       </c>
       <c r="G49" s="3">
         <v>4100</v>
       </c>
       <c r="H49" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I49" s="3">
         <v>4200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4900</v>
-      </c>
-      <c r="K49" s="3">
-        <v>2600</v>
       </c>
       <c r="L49" s="3">
         <v>2600</v>
@@ -3681,22 +3792,22 @@
         <v>2600</v>
       </c>
       <c r="N49" s="3">
-        <v>1900</v>
+        <v>2600</v>
       </c>
       <c r="O49" s="3">
         <v>1900</v>
       </c>
       <c r="P49" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="Q49" s="3">
         <v>2000</v>
       </c>
       <c r="R49" s="3">
+        <v>2000</v>
+      </c>
+      <c r="S49" s="3">
         <v>1800</v>
-      </c>
-      <c r="S49" s="3">
-        <v>1400</v>
       </c>
       <c r="T49" s="3">
         <v>1400</v>
@@ -3705,7 +3816,7 @@
         <v>1400</v>
       </c>
       <c r="V49" s="3">
-        <v>300</v>
+        <v>1400</v>
       </c>
       <c r="W49" s="3">
         <v>300</v>
@@ -3714,7 +3825,7 @@
         <v>300</v>
       </c>
       <c r="Y49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Z49" s="3">
         <v>200</v>
@@ -3725,8 +3836,11 @@
       <c r="AB49" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,8 +4002,11 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3894,7 +4014,7 @@
         <v>100</v>
       </c>
       <c r="E52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F52" s="3">
         <v>200</v>
@@ -3906,13 +4026,13 @@
         <v>200</v>
       </c>
       <c r="I52" s="3">
+        <v>200</v>
+      </c>
+      <c r="J52" s="3">
         <v>300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>200</v>
-      </c>
-      <c r="K52" s="3">
-        <v>100</v>
       </c>
       <c r="L52" s="3">
         <v>100</v>
@@ -3921,7 +4041,7 @@
         <v>100</v>
       </c>
       <c r="N52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
@@ -3965,8 +4085,11 @@
       <c r="AB52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,88 +4168,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E54" s="3">
         <v>18000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>18800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>24800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>28500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>31700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>30900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>30600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>35800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>40100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>44200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>48700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>51300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>45600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>48800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>49400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>39000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>19300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>20400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>22100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>23500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,22 +4315,23 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>700</v>
+      </c>
+      <c r="E57" s="3">
         <v>500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1300</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1100</v>
       </c>
       <c r="H57" s="3">
         <v>1100</v>
@@ -4209,78 +4340,81 @@
         <v>1100</v>
       </c>
       <c r="J57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K57" s="3">
         <v>1500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1900</v>
-      </c>
-      <c r="L57" s="3">
-        <v>1400</v>
       </c>
       <c r="M57" s="3">
         <v>1400</v>
       </c>
       <c r="N57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O57" s="3">
         <v>900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1200</v>
-      </c>
-      <c r="V57" s="3">
-        <v>800</v>
       </c>
       <c r="W57" s="3">
         <v>800</v>
       </c>
       <c r="X57" s="3">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="Y57" s="3">
         <v>400</v>
       </c>
       <c r="Z57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA57" s="3">
         <v>700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="E58" s="3">
         <v>600</v>
       </c>
       <c r="F58" s="3">
+        <v>600</v>
+      </c>
+      <c r="G58" s="3">
         <v>500</v>
-      </c>
-      <c r="G58" s="3">
-        <v>600</v>
       </c>
       <c r="H58" s="3">
         <v>600</v>
@@ -4289,7 +4423,7 @@
         <v>600</v>
       </c>
       <c r="J58" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="K58" s="3">
         <v>100</v>
@@ -4298,7 +4432,7 @@
         <v>100</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -4321,17 +4455,17 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="V58" s="3">
-        <v>200</v>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W58" s="3">
         <v>200</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>10</v>
+      <c r="X58" s="3">
+        <v>200</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>10</v>
@@ -4345,201 +4479,210 @@
       <c r="AB58" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>11600</v>
+        <v>700</v>
       </c>
       <c r="E59" s="3">
+        <v>12200</v>
+      </c>
+      <c r="F59" s="3">
         <v>11200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>21300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1700</v>
-      </c>
-      <c r="N59" s="3">
-        <v>1200</v>
       </c>
       <c r="O59" s="3">
         <v>1200</v>
       </c>
       <c r="P59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Q59" s="3">
         <v>1000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>700</v>
-      </c>
-      <c r="W59" s="3">
-        <v>600</v>
       </c>
       <c r="X59" s="3">
         <v>600</v>
       </c>
       <c r="Y59" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z59" s="3">
         <v>700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>500</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>300</v>
       </c>
       <c r="AB59" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E60" s="3">
         <v>13800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>16200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>23500</v>
-      </c>
-      <c r="J60" s="3">
-        <v>10800</v>
       </c>
       <c r="K60" s="3">
         <v>10800</v>
       </c>
       <c r="L60" s="3">
+        <v>10800</v>
+      </c>
+      <c r="M60" s="3">
         <v>3400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="E61" s="3">
         <v>1600</v>
       </c>
       <c r="F61" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G61" s="3">
         <v>1700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1600</v>
-      </c>
-      <c r="H61" s="3">
-        <v>1700</v>
       </c>
       <c r="I61" s="3">
         <v>1700</v>
       </c>
       <c r="J61" s="3">
-        <v>100</v>
+        <v>1700</v>
       </c>
       <c r="K61" s="3">
         <v>100</v>
       </c>
       <c r="L61" s="3">
+        <v>100</v>
+      </c>
+      <c r="M61" s="3">
         <v>200</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -4565,14 +4708,14 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>300</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4585,8 +4728,11 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4617,8 +4763,8 @@
       <c r="L62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M62" s="3">
-        <v>400</v>
+      <c r="M62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N62" s="3">
         <v>400</v>
@@ -4630,16 +4776,16 @@
         <v>400</v>
       </c>
       <c r="Q62" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="R62" s="3">
         <v>100</v>
       </c>
       <c r="S62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U62" s="3">
         <v>100</v>
@@ -4654,7 +4800,7 @@
         <v>100</v>
       </c>
       <c r="Y62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z62" s="3">
         <v>200</v>
@@ -4663,10 +4809,13 @@
         <v>200</v>
       </c>
       <c r="AB62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,88 +5060,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E66" s="3">
         <v>15400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>17900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>20300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>25300</v>
-      </c>
-      <c r="J66" s="3">
-        <v>11100</v>
       </c>
       <c r="K66" s="3">
         <v>11100</v>
       </c>
       <c r="L66" s="3">
+        <v>11100</v>
+      </c>
+      <c r="M66" s="3">
         <v>3700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5193,17 +5361,17 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
         <v>2000</v>
       </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
       <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
         <v>2000</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,88 +5506,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-105100</v>
+        <v>-109000</v>
       </c>
       <c r="E72" s="3">
         <v>-105100</v>
       </c>
       <c r="F72" s="3">
+        <v>-105100</v>
+      </c>
+      <c r="G72" s="3">
         <v>-97300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-99000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-98100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-98000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-79400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-76400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-71400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-67400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-63800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-60000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-55200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-49800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-44500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-38500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-30700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-25300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-21800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-17900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-15100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-12700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-7800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-5900</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +5838,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E76" s="3">
         <v>2600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>23600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>27100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>30000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>32900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>36900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>41300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>45500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>48800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>42100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>46400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>47400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>37100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>18100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>19200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>20700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>22500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E81" s="3">
         <v>100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-7600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-18400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-6000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,13 +6208,14 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
         <v>200</v>
@@ -6028,13 +6227,13 @@
         <v>200</v>
       </c>
       <c r="H83" s="3">
+        <v>200</v>
+      </c>
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>300</v>
-      </c>
-      <c r="J83" s="3">
-        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
@@ -6043,7 +6242,7 @@
         <v>100</v>
       </c>
       <c r="M83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N83" s="3">
         <v>200</v>
@@ -6055,7 +6254,7 @@
         <v>200</v>
       </c>
       <c r="Q83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R83" s="3">
         <v>100</v>
@@ -6070,7 +6269,7 @@
         <v>100</v>
       </c>
       <c r="V83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
@@ -6090,8 +6289,11 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6704,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-12100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-5800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2700</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-2100</v>
       </c>
       <c r="AA89" s="3">
         <v>-2100</v>
       </c>
       <c r="AB89" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,8 +6820,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6621,7 +6842,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
@@ -6630,46 +6851,46 @@
         <v>-100</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-800</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-100</v>
       </c>
       <c r="O91" s="3">
         <v>-100</v>
       </c>
       <c r="P91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1000</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-200</v>
       </c>
       <c r="T91" s="3">
         <v>-200</v>
       </c>
       <c r="U91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
       <c r="Y91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z91" s="3">
         <v>-100</v>
@@ -6678,10 +6899,13 @@
         <v>-100</v>
       </c>
       <c r="AB91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,8 +7067,11 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6852,58 +7082,58 @@
         <v>-100</v>
       </c>
       <c r="F94" s="3">
-        <v>2500</v>
+        <v>-100</v>
       </c>
       <c r="G94" s="3">
         <v>2500</v>
       </c>
       <c r="H94" s="3">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="I94" s="3">
         <v>2400</v>
       </c>
       <c r="J94" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K94" s="3">
         <v>-4400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>7200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>5100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>5000</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>4900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>4700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-10200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-25100</v>
-      </c>
-      <c r="W94" s="3">
-        <v>-100</v>
       </c>
       <c r="X94" s="3">
         <v>-100</v>
@@ -6920,8 +7150,11 @@
       <c r="AB94" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,31 +7183,32 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>10</v>
+      <c r="E96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="3">
+        <v>0</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H96" s="3">
-        <v>100</v>
+      <c r="H96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="I96" s="3">
         <v>100</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>10</v>
+      <c r="J96" s="3">
+        <v>100</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>10</v>
@@ -6982,8 +7216,8 @@
       <c r="L96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,40 +7513,43 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>5700</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>9800</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -7312,46 +7558,49 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>1300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>12100</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>1800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>13700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>21600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>100</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7382,8 +7631,8 @@
       <c r="L101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7430,84 +7679,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>11100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-14600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-15300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>19900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>10700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WRAP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WRAP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="92">
   <si>
     <t>WRAP</t>
   </si>
@@ -656,391 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F8" s="3">
         <v>1500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>3600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>3600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>2400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>700</v>
+      </c>
+      <c r="F9" s="3">
         <v>600</v>
-      </c>
-      <c r="E9" s="3">
-        <v>500</v>
-      </c>
-      <c r="F9" s="3">
-        <v>200</v>
       </c>
       <c r="G9" s="3">
         <v>500</v>
       </c>
       <c r="H9" s="3">
+        <v>200</v>
+      </c>
+      <c r="I9" s="3">
+        <v>500</v>
+      </c>
+      <c r="J9" s="3">
         <v>400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>2000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>200</v>
       </c>
-      <c r="AC9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>700</v>
+      </c>
+      <c r="F10" s="3">
         <v>900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>1000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>-300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>2200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>500</v>
-      </c>
-      <c r="R10" s="3">
-        <v>700</v>
-      </c>
-      <c r="S10" s="3">
-        <v>700</v>
       </c>
       <c r="T10" s="3">
         <v>700</v>
       </c>
       <c r="U10" s="3">
+        <v>700</v>
+      </c>
+      <c r="V10" s="3">
+        <v>700</v>
+      </c>
+      <c r="W10" s="3">
         <v>-100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>500</v>
-      </c>
-      <c r="X10" s="3">
-        <v>300</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>200</v>
       </c>
       <c r="Z10" s="3">
         <v>300</v>
       </c>
       <c r="AA10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB10" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AC10" s="3">
         <v>100</v>
       </c>
       <c r="AD10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1071,94 +1096,102 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F12" s="3">
         <v>200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>1200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>1900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>2100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>1200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>1100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>900</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>600</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>500</v>
       </c>
       <c r="AA12" s="3">
         <v>600</v>
       </c>
       <c r="AB12" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="AC12" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AD12" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF12" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1243,41 +1276,47 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>10</v>
+      <c r="D14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E14" s="3">
+        <v>600</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="3">
         <v>1600</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M14" s="3">
         <v>1700</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1293,27 +1332,27 @@
       <c r="R14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>10</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-400</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1329,13 +1368,19 @@
       <c r="AD14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
         <v>100</v>
@@ -1344,7 +1389,7 @@
         <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
         <v>200</v>
@@ -1356,23 +1401,23 @@
         <v>200</v>
       </c>
       <c r="K15" s="3">
+        <v>200</v>
+      </c>
+      <c r="L15" s="3">
+        <v>200</v>
+      </c>
+      <c r="M15" s="3">
         <v>100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>200</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1415,8 +1460,14 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1495,194 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F17" s="3">
         <v>4300</v>
-      </c>
-      <c r="E17" s="3">
-        <v>3900</v>
-      </c>
-      <c r="F17" s="3">
-        <v>4700</v>
       </c>
       <c r="G17" s="3">
         <v>3900</v>
       </c>
       <c r="H17" s="3">
+        <v>4700</v>
+      </c>
+      <c r="I17" s="3">
+        <v>3900</v>
+      </c>
+      <c r="J17" s="3">
         <v>4200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>4700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>5600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>5500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>6400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>6300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>5000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>7200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>5600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>5900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>7000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>7700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>7800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>9700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>7000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>5000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>4900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>3700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>3100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>2800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>2000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-2900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-3900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-3000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-3600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-3200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-4100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-4900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-2800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-5100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-4300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-3600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-4700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-5400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-5300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-6000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-7800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-5500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-3600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,8 +1713,10 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1657,171 +1724,183 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-4000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>3000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-5600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-2700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-4200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>11700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-3600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-5800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>2200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-16500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-2600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-4900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-4100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-3300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-4600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-5200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-5100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-5900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-7700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-5300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-3500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1867,11 +1946,11 @@
       <c r="Q22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -1891,8 +1970,8 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>10</v>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
@@ -1900,100 +1979,112 @@
       <c r="AB22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>10</v>
+      <c r="AC22" s="3">
+        <v>0</v>
       </c>
       <c r="AD22" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF22" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-3700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-7600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>2000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-18400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-2800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-5000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-4000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-3500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-4800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-5400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-5200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-6000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-7800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-5400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-3600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2030,11 +2121,11 @@
       <c r="N24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2078,8 +2169,14 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2261,198 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-3700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-7600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>2000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-18400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-2800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-5000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-4000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-3500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-4800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-5400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-5200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-6000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-7800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-5400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-3600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-3900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-7800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-18600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-3000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-5000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-4000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-3500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-4800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-5400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-5200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-6000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-7800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-5400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-3600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2537,14 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,8 +2629,14 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2721,14 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,8 +2813,14 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2689,171 +2828,183 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>4000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-3000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>5600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>2700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>4200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-11700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-3700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-7600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>2000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-18400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-2800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-5000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-4000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-3500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-4800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-5400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-5200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-6000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-7800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-5400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-3600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3089,203 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-3700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-7600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>2000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-18400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-2800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-5000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-4000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-3500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-4800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-5400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-5200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-6000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-7800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-5400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-3600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3316,10 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,94 +3350,102 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F41" s="3">
         <v>6000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>4200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>6200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>4000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>4900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>11700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>9500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>5300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>3800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>3600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>5000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>4900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>9900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>13100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>2000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>16600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>20100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>35400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>15500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>17000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>19300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>21400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3286,59 +3465,59 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>2500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>5000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>7500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>10000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>6500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>6500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>13900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>19900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>24900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>25000</v>
-      </c>
-      <c r="S42" s="3">
-        <v>30000</v>
-      </c>
-      <c r="T42" s="3">
-        <v>30000</v>
       </c>
       <c r="U42" s="3">
         <v>30000</v>
       </c>
       <c r="V42" s="3">
+        <v>30000</v>
+      </c>
+      <c r="W42" s="3">
+        <v>30000</v>
+      </c>
+      <c r="X42" s="3">
         <v>35000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>25000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>25000</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z42" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA42" s="3" t="s">
         <v>10</v>
       </c>
@@ -3351,180 +3530,198 @@
       <c r="AD42" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF42" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F43" s="3">
         <v>1800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>3300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>3000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>4300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>2800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>2200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>4200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>3900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>3300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>2600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>2200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>200</v>
-      </c>
-      <c r="AB43" s="3">
-        <v>100</v>
-      </c>
-      <c r="AC43" s="3">
-        <v>0</v>
       </c>
       <c r="AD43" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F44" s="3">
         <v>5500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>5900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>6100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>6200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>6300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>6500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>6400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>5800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>5800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>6500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>5600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>4000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>3000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>2000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>1900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>1600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>2300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>2800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>3600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>2700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>2000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>2100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>2300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>2200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>2000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>1300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3561,38 +3758,38 @@
       <c r="N45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q45" s="3">
         <v>800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>500</v>
-      </c>
-      <c r="U45" s="3">
-        <v>800</v>
-      </c>
-      <c r="V45" s="3">
-        <v>800</v>
       </c>
       <c r="W45" s="3">
         <v>800</v>
       </c>
       <c r="X45" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="Y45" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="Z45" s="3">
         <v>300</v>
@@ -3601,102 +3798,114 @@
         <v>300</v>
       </c>
       <c r="AB45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD45" s="3">
         <v>100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F46" s="3">
         <v>13600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>11300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>13500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>10500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>12200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>15000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>17700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>21200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>25800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>27400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>23600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>26900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>29500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>32600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>36800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>41200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>45900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>49300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>43600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>46900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>48500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>38200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>18500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>19700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>21400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>22900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3733,11 +3942,11 @@
       <c r="N47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3781,73 +3990,79 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F48" s="3">
         <v>2400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>600</v>
-      </c>
-      <c r="W48" s="3">
-        <v>500</v>
-      </c>
-      <c r="X48" s="3">
-        <v>500</v>
       </c>
       <c r="Y48" s="3">
         <v>500</v>
@@ -3862,90 +4077,96 @@
         <v>500</v>
       </c>
       <c r="AC48" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD48" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE48" s="3">
         <v>400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F49" s="3">
         <v>2100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>2300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>2300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>2400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>4100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>4100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>4200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>4300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>4900</v>
-      </c>
-      <c r="M49" s="3">
-        <v>2600</v>
-      </c>
-      <c r="N49" s="3">
-        <v>2600</v>
       </c>
       <c r="O49" s="3">
         <v>2600</v>
       </c>
       <c r="P49" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>2600</v>
+      </c>
+      <c r="R49" s="3">
         <v>1900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>2000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>2000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>1800</v>
-      </c>
-      <c r="U49" s="3">
-        <v>1400</v>
-      </c>
-      <c r="V49" s="3">
-        <v>1400</v>
       </c>
       <c r="W49" s="3">
         <v>1400</v>
       </c>
       <c r="X49" s="3">
-        <v>300</v>
+        <v>1400</v>
       </c>
       <c r="Y49" s="3">
-        <v>300</v>
+        <v>1400</v>
       </c>
       <c r="Z49" s="3">
         <v>300</v>
       </c>
       <c r="AA49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AB49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AC49" s="3">
         <v>200</v>
@@ -3953,8 +4174,14 @@
       <c r="AD49" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF49" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4266,14 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,8 +4358,14 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4140,10 +4379,10 @@
         <v>100</v>
       </c>
       <c r="G52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I52" s="3">
         <v>200</v>
@@ -4152,25 +4391,25 @@
         <v>200</v>
       </c>
       <c r="K52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L52" s="3">
         <v>200</v>
       </c>
       <c r="M52" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="N52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O52" s="3">
         <v>100</v>
       </c>
       <c r="P52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
@@ -4211,8 +4450,14 @@
       <c r="AD52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,94 +4542,106 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>15400</v>
+      </c>
+      <c r="F54" s="3">
         <v>18200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>15600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>18000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>15100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>18800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>21800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>24800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>28500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>31700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>30900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>27200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>30600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>32500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>35800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>40100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>44200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>48700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>51300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>45600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>48800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>49400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>39000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>19300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>20400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>22100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>23500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4672,10 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,85 +4706,87 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>800</v>
+      </c>
+      <c r="E57" s="3">
         <v>600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
+        <v>600</v>
+      </c>
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1300</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1100</v>
       </c>
       <c r="K57" s="3">
         <v>1100</v>
       </c>
       <c r="L57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N57" s="3">
         <v>1500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1400</v>
-      </c>
-      <c r="O57" s="3">
-        <v>1400</v>
-      </c>
-      <c r="P57" s="3">
-        <v>900</v>
       </c>
       <c r="Q57" s="3">
         <v>1400</v>
       </c>
       <c r="R57" s="3">
+        <v>900</v>
+      </c>
+      <c r="S57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="T57" s="3">
         <v>1700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>2400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>400</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>400</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>700</v>
       </c>
       <c r="AC57" s="3">
         <v>400</v>
@@ -4533,49 +4794,55 @@
       <c r="AD57" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF57" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>100</v>
+      </c>
+      <c r="E58" s="3">
         <v>300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
+        <v>300</v>
+      </c>
+      <c r="G58" s="3">
         <v>200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>600</v>
-      </c>
-      <c r="G58" s="3">
-        <v>600</v>
-      </c>
-      <c r="H58" s="3">
-        <v>500</v>
       </c>
       <c r="I58" s="3">
         <v>600</v>
       </c>
       <c r="J58" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="K58" s="3">
         <v>600</v>
       </c>
       <c r="L58" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="M58" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="N58" s="3">
         <v>100</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -4595,21 +4862,21 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>10</v>
+      <c r="W58" s="3">
+        <v>0</v>
       </c>
       <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z58" s="3">
         <v>200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>200</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA58" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>10</v>
       </c>
@@ -4619,94 +4886,106 @@
       <c r="AD58" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF58" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>500</v>
+      </c>
+      <c r="E59" s="3">
         <v>800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
+        <v>800</v>
+      </c>
+      <c r="G59" s="3">
         <v>700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>12200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>11200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>8800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>14200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>16400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>21300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>8400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>8000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4714,102 +4993,108 @@
         <v>1900</v>
       </c>
       <c r="E60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F60" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G60" s="3">
         <v>2000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>13800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>13200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>10700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>16200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>18500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>23500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>10800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>10800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>3200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>2200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>2800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>2900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>3100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>2600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>3400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>2300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>1100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>1300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F61" s="3">
         <v>2200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1600</v>
-      </c>
-      <c r="G61" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H61" s="3">
-        <v>1700</v>
       </c>
       <c r="I61" s="3">
         <v>1600</v>
@@ -4818,23 +5103,23 @@
         <v>1700</v>
       </c>
       <c r="K61" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L61" s="3">
         <v>1700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N61" s="3">
         <v>100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>200</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4857,17 +5142,17 @@
         <v>0</v>
       </c>
       <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>300</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -4877,8 +5162,14 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4915,11 +5206,11 @@
       <c r="N62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O62" s="3">
-        <v>400</v>
-      </c>
-      <c r="P62" s="3">
-        <v>400</v>
+      <c r="O62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q62" s="3">
         <v>400</v>
@@ -4928,19 +5219,19 @@
         <v>400</v>
       </c>
       <c r="S62" s="3">
+        <v>400</v>
+      </c>
+      <c r="T62" s="3">
+        <v>400</v>
+      </c>
+      <c r="U62" s="3">
         <v>100</v>
-      </c>
-      <c r="T62" s="3">
-        <v>100</v>
-      </c>
-      <c r="U62" s="3">
-        <v>0</v>
       </c>
       <c r="V62" s="3">
         <v>100</v>
       </c>
       <c r="W62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X62" s="3">
         <v>100</v>
@@ -4952,19 +5243,25 @@
         <v>100</v>
       </c>
       <c r="AA62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC62" s="3">
         <v>200</v>
       </c>
       <c r="AD62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AE62" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5346,14 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5438,14 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,55 +5530,61 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4100</v>
+        <v>2300</v>
       </c>
       <c r="E66" s="3">
         <v>3900</v>
       </c>
       <c r="F66" s="3">
+        <v>4100</v>
+      </c>
+      <c r="G66" s="3">
+        <v>3900</v>
+      </c>
+      <c r="H66" s="3">
         <v>15400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>14900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>12400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>17900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>20300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>25300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>11100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>11100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>3500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>2600</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>3000</v>
-      </c>
-      <c r="R66" s="3">
-        <v>3200</v>
       </c>
       <c r="S66" s="3">
         <v>3000</v>
@@ -5278,37 +5593,43 @@
         <v>3200</v>
       </c>
       <c r="U66" s="3">
+        <v>3000</v>
+      </c>
+      <c r="V66" s="3">
+        <v>3200</v>
+      </c>
+      <c r="W66" s="3">
         <v>2600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>3500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>2400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>2000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5660,10 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5748,14 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5840,14 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5535,7 +5870,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -5547,7 +5882,7 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="O70" s="3">
         <v>0</v>
@@ -5597,8 +5932,14 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,94 +6024,106 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-121100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-116300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-112000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-109000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-105100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-105100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-97300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-99000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-98100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-98000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-79400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-76400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-71400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-67400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-63800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-60000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-55200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-49800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-44500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-38500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-30700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-25300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-21800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-17900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-15100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-12700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-7800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-5900</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6208,14 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6300,14 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,94 +6392,106 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>11500</v>
+      </c>
+      <c r="F76" s="3">
         <v>14100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>11800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>6400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>3200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>18500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>19800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>23600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>27100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>30000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>32900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>36900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>41300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>45500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>48800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>42100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>46400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>47400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>37100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>18100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>19200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>20700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>22500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6576,203 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-3700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-7600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>2000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-18400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-2800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-5000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-4000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-3500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-4800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-5400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-5200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-6000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-7800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-5400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-3600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,16 +6803,18 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
@@ -6432,25 +6829,25 @@
         <v>200</v>
       </c>
       <c r="J83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L83" s="3">
         <v>100</v>
       </c>
       <c r="M83" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="N83" s="3">
         <v>100</v>
       </c>
       <c r="O83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q83" s="3">
         <v>200</v>
@@ -6459,10 +6856,10 @@
         <v>200</v>
       </c>
       <c r="S83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U83" s="3">
         <v>100</v>
@@ -6474,10 +6871,10 @@
         <v>100</v>
       </c>
       <c r="X83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
@@ -6494,8 +6891,14 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6983,14 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +7075,14 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +7167,14 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7259,14 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,94 +7351,106 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-3100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-3500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-3700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-3800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-12100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>2300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-3100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-3600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-4900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-4500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-3500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-5800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-4400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-4500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,20 +7481,22 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
@@ -7069,67 +7510,73 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
       </c>
       <c r="N91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-1000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
       <c r="AA91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC91" s="3">
         <v>-100</v>
       </c>
       <c r="AD91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AE91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7661,14 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,8 +7753,14 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7318,61 +7777,61 @@
         <v>-100</v>
       </c>
       <c r="H94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J94" s="3">
         <v>2500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>2500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>2400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>2400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-4400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>7200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>5100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>5000</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>4900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-1000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>4700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-10200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-25100</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>-100</v>
       </c>
       <c r="AA94" s="3">
         <v>-100</v>
@@ -7386,8 +7845,14 @@
       <c r="AD94" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF94" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,8 +7883,10 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7432,8 +7899,8 @@
       <c r="F96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>10</v>
@@ -7441,26 +7908,26 @@
       <c r="I96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L96" s="3">
         <v>100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>100</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="N96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7504,8 +7971,14 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +8063,14 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +8155,14 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,94 +8247,106 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>300</v>
+      </c>
+      <c r="F100" s="3">
         <v>4500</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>5700</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>9800</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="O100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>1300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>12100</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>1800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>13700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>21600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>100</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD100" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7886,11 +8383,11 @@
       <c r="N101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -7934,90 +8431,102 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F102" s="3">
         <v>1800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-2000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>2600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>2800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-6800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>2200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>4200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-4900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-3200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>11100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-14600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-3500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-15300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>19900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>10700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-1700</v>
       </c>
     </row>
